--- a/cases/AConly_case14_tapctrl.xlsx
+++ b/cases/AConly_case14_tapctrl.xlsx
@@ -1111,7 +1111,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1130,7 +1130,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1605,7 +1604,7 @@
       </c>
       <c r="V1" s="4" t="inlineStr">
         <is>
-          <t>Shunt Steps</t>
+          <t>Shunt Step Size [Mvar]</t>
         </is>
       </c>
     </row>
@@ -2479,7 +2478,7 @@
       </c>
       <c r="S1" s="4" t="inlineStr">
         <is>
-          <t>Ctrl Steps</t>
+          <t>Ctrl Step Size</t>
         </is>
       </c>
     </row>
